--- a/outputs/remal/Ablation_Kappa_Comparison/Remal_Ablation_Kappa_Comparison.xlsx
+++ b/outputs/remal/Ablation_Kappa_Comparison/Remal_Ablation_Kappa_Comparison.xlsx
@@ -5273,7 +5273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -5333,154 +5333,189 @@
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Weighted_Hazard = 0.35*Norm_Wind Gust + 0.35*Norm_Rainfall + 0.30*Norm_Storm Surge</t>
+          <t>Weighted_Hazard = w_wind*Norm_Wind Gust + w_rain*Norm_Rainfall + w_surge*Norm_Storm Surge</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>Equivalent Excel columns: 0.35*H + 0.35*J + 0.30*L.</t>
+          <t>Equivalent Excel columns: w_wind*H + w_rain*J + w_surge*L.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr"/>
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Weights used for Remal (see HAZARD_WEIGHTS in the script):</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Forecast severity boundaries:</t>
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1dlt: w_wind=0.35, w_rain=0.35, w_surge=0.3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>Derived independently for each lead exactly as in the repository.</t>
+          <t xml:space="preserve">  2dlt: w_wind=0.35, w_rain=0.35, w_surge=0.3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>House: from Norm_Impact_House using Excel AG class labels.</t>
+          <t xml:space="preserve">  3dlt: w_wind=0.35, w_rain=0.35, w_surge=0.3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>Agriculture: from Norm_Impact_fAPAR using Excel X class labels.</t>
+          <t>Weights differ by cyclone and by lead time and are set manually in HAZARD_WEIGHTS.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Thresholds are rounded to 4 decimals before classification.</t>
-        </is>
-      </c>
+      <c r="A17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>The same lead-specific sector boundary set is applied to Composite, Vulnerability-only and Hazard-only.</t>
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Forecast severity boundaries:</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr"/>
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Derived independently for each lead exactly as in the repository.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>DDM calibration:</t>
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>House: from Norm_Impact_House using Excel AG class labels.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>Zero = No Impact.</t>
+          <t>Agriculture: from Norm_Impact_fAPAR using Excel X class labels.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>Positive DDM values are exhaustively searched for Low/High cut pairs.</t>
+          <t>Thresholds are rounded to 4 decimals before classification.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>For each candidate pair, QWK is calculated separately for 1dlt, 2dlt and 3dlt.</t>
+          <t>The same lead-specific sector boundary set is applied to Composite, Vulnerability-only and Hazard-only.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>The mean of the three Kappas is maximized.</t>
-        </is>
-      </c>
+      <c r="A24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>The selected Low/High pair is then fixed for all three leads for that predictor and damage variable.</t>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>DDM calibration:</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>The maximum positive observed DDM value is excluded as a High cut so that the High class remains populated.</t>
+          <t>Zero = No Impact.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr"/>
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Positive DDM values are exhaustively searched for Low/High cut pairs.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>Agreement table:</t>
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>For each candidate pair, QWK is calculated separately for 1dlt, 2dlt and 3dlt.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>Exact = difference of 0 classes.</t>
+          <t>The mean of the three Kappas is maximized.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>Adjacent = difference of exactly 1 class.</t>
+          <t>The selected Low/High pair is then fixed for all three leads for that predictor and damage variable.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
+          <t>The maximum positive observed DDM value is excluded as a High cut so that the High class remains populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Agreement table:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>Exact = difference of 0 classes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Adjacent = difference of exactly 1 class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
           <t>Off-Cat. = difference of 2 or more classes.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>Exact + Adjacent + Off-Cat. = 100%.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Repository Within-1 % = Exact % + Adjacent %.</t>
         </is>
